--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488160_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488160_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5205</v>
+        <v>10.7394</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4412</v>
+        <v>7.2908</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0793</v>
+        <v>3.4486</v>
       </c>
       <c r="G2" t="n">
         <v>3.7101</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3368</v>
+        <v>-0.1178</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1279</v>
+        <v>-0.2782</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2089</v>
+        <v>0.1604</v>
       </c>
       <c r="V2" t="n">
         <v>5.6648</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5797</v>
+        <v>3.851</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5186</v>
+        <v>1.7898</v>
       </c>
       <c r="F3" t="n">
         <v>2.0612</v>
@@ -688,10 +688,10 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1899</v>
+        <v>1.4612</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4326</v>
+        <v>0.7039</v>
       </c>
       <c r="U3" t="n">
         <v>0.7573</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5502</v>
+        <v>3.4259</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4535</v>
+        <v>2.3236</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0967</v>
+        <v>1.1024</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6599</v>
+        <v>1.2035</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1072</v>
+        <v>0.3482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5527</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7496</v>
+        <v>0.8551</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0434</v>
+        <v>0.1074</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7063</v>
+        <v>0.7477</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0897</v>
+        <v>0.3485</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0639</v>
+        <v>0.2409</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1536</v>
+        <v>0.1076</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2221</v>
+        <v>-0.4076</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7039</v>
+        <v>-0.1228</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4818</v>
+        <v>-0.2848</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0005</v>
+        <v>1.8888</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.875</v>
+        <v>3.2438</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9204</v>
+        <v>2.0733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9546</v>
+        <v>1.1705</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2035</v>
+        <v>1.6599</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3482</v>
+        <v>1.1072</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.5527</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8551</v>
+        <v>1.7496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1074</v>
+        <v>1.0434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7477</v>
+        <v>0.7063</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3485</v>
+        <v>-0.0897</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2409</v>
+        <v>0.0639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1076</v>
+        <v>-0.1536</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9585</v>
+        <v>-0.0843</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.526</v>
+        <v>0.3236</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4325</v>
+        <v>-0.4079</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8888</v>
+        <v>0.0005</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0901</v>
+        <v>3.1619</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4917</v>
+        <v>1.609</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5818</v>
+        <v>1.5528</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0202</v>
+        <v>1.4458</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0678</v>
+        <v>-0.8397</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0476</v>
+        <v>2.2854</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1816</v>
+        <v>1.5875</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7514999999999999</v>
+        <v>-0.3523</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5699</v>
+        <v>1.9397</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8386</v>
+        <v>-0.1417</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3163</v>
+        <v>-0.4874</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5223</v>
+        <v>0.3457</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1117</v>
+        <v>2.9646</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8677</v>
+        <v>-0.3221</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2363</v>
+        <v>-0.3109</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6315</v>
+        <v>-0.0112</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9433</v>
+        <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8696</v>
+        <v>1.7213</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6614</v>
+        <v>-0.5896</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2081</v>
+        <v>2.3109</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4458</v>
+        <v>1.0202</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8397</v>
+        <v>1.0678</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2854</v>
+        <v>-0.0476</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5875</v>
+        <v>0.1816</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3523</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9397</v>
+        <v>-0.5699</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1417</v>
+        <v>0.8386</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4874</v>
+        <v>0.3163</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3457</v>
+        <v>0.5223</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0382</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9646</v>
+        <v>1.1117</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6144</v>
+        <v>0.499</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2584</v>
+        <v>0.1384</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3559</v>
+        <v>0.3606</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2589</v>
+        <v>0.9433</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6593</v>
+        <v>0.7086</v>
       </c>
       <c r="E9" t="n">
         <v>0.9253</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.266</v>
+        <v>-0.2168</v>
       </c>
       <c r="G9" t="n">
         <v>0.4973</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1525</v>
+        <v>-0.1032</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0746</v>
+        <v>0.5004</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0659</v>
+        <v>-2.5648</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9913</v>
+        <v>3.0652</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0544</v>
@@ -1234,13 +1234,13 @@
         <v>2.4087</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.279</v>
+        <v>0.296</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.0497</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2718</v>
+        <v>0.3457</v>
       </c>
       <c r="V10" t="n">
         <v>0.6294</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4334</v>
+        <v>-1.5872</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0488</v>
+        <v>-2.4752</v>
       </c>
       <c r="F11" t="n">
-        <v>4.6154</v>
+        <v>0.8879</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.9209</v>
+        <v>-0.1515</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.649</v>
+        <v>-1.0179</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2718</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8721</v>
+        <v>-0.7289</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.3851</v>
+        <v>-0.8119</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.487</v>
+        <v>0.0829</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0488</v>
+        <v>0.5774</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.264</v>
+        <v>-0.206</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2152</v>
+        <v>0.7834</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>2.594</v>
+        <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3578</v>
+        <v>0.1937</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9176</v>
+        <v>0.1066</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4402</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.003</v>
+        <v>-2.6185</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9648</v>
+        <v>-6.3968</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9618</v>
+        <v>3.7783</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1515</v>
+        <v>-3.9209</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0179</v>
+        <v>-3.649</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8663999999999999</v>
+        <v>-0.2718</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7289</v>
+        <v>-3.8721</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8119</v>
+        <v>-3.3851</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0829</v>
+        <v>-0.487</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5774</v>
+        <v>-0.0488</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.206</v>
+        <v>-0.264</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7834</v>
+        <v>0.2152</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4823</v>
+        <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2221</v>
+        <v>1.1727</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.383</v>
+        <v>0.5696</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1609</v>
+        <v>0.6031</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2018</v>
+        <v>-2.902</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9003</v>
+        <v>-0.6498</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3014</v>
+        <v>-2.2522</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7375</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.5726</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4377</v>
+        <v>-0.1871</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4347</v>
+        <v>-0.3855</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5183</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.3108</v>
+        <v>-3.0296</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4018</v>
+        <v>0.6091</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7126</v>
+        <v>-3.6387</v>
       </c>
       <c r="G14" t="n">
         <v>1.8381</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0961</v>
+        <v>-0.8148</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.766</v>
+        <v>-0.5586</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.33</v>
+        <v>-0.2562</v>
       </c>
       <c r="V14" t="n">
         <v>-5.3498</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>17.7091</v>
+        <v>18.8033</v>
       </c>
       <c r="E15" t="n">
-        <v>4.439</v>
+        <v>5.533000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>13.2702</v>
+        <v>13.2701</v>
       </c>
       <c r="G15" t="n">
         <v>11.1356</v>
@@ -1597,7 +1597,7 @@
         <v>6.565799999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>7.8398</v>
+        <v>7.839800000000001</v>
       </c>
       <c r="K15" t="n">
         <v>5.614000000000002</v>
@@ -1624,16 +1624,16 @@
         <v>20.3815</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1056000000000001</v>
+        <v>1.2002</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8141999999999998</v>
+        <v>0.2800999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9201999999999999</v>
+        <v>0.9200000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9440999999999997</v>
+        <v>-0.9440999999999988</v>
       </c>
       <c r="W15" t="n">
         <v>10.3835</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3647</v>
+        <v>6.0828</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1585</v>
+        <v>2.7461</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2061</v>
+        <v>3.3367</v>
       </c>
       <c r="G16" t="n">
         <v>0.0247</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.011</v>
+        <v>-0.2929</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0943</v>
+        <v>-0.5067</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0833</v>
+        <v>0.2139</v>
       </c>
       <c r="V16" t="n">
         <v>5.9804</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1609</v>
+        <v>2.4082</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1484</v>
+        <v>2.9602</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0125</v>
+        <v>-0.5521</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1994</v>
+        <v>-1.5151</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4596</v>
+        <v>-0.202</v>
       </c>
       <c r="I17" t="n">
-        <v>0.659</v>
+        <v>-1.3131</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5162</v>
+        <v>0.4335</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8112</v>
+        <v>0.4335</v>
       </c>
       <c r="L17" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3168</v>
+        <v>-1.9485</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2708</v>
+        <v>-0.6354</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.046</v>
+        <v>-1.3131</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3321</v>
+        <v>0.4443</v>
       </c>
       <c r="T17" t="n">
-        <v>0.485</v>
+        <v>0.1595</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8471</v>
+        <v>0.2848</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2589</v>
+        <v>4.4054</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2589</v>
+        <v>4.4054</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8754</v>
+        <v>2.113</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0582</v>
+        <v>1.5608</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1827</v>
+        <v>0.5522</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5151</v>
+        <v>0.1994</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.202</v>
+        <v>-0.4596</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3131</v>
+        <v>0.659</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4335</v>
+        <v>1.5162</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4335</v>
+        <v>0.8112</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9485</v>
+        <v>-1.3168</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6354</v>
+        <v>-1.2708</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3131</v>
+        <v>-0.046</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9115</v>
+        <v>0.2841</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2574</v>
+        <v>-0.1026</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6541</v>
+        <v>0.3867</v>
       </c>
       <c r="V18" t="n">
-        <v>4.4054</v>
+        <v>1.2589</v>
       </c>
       <c r="W18" t="n">
-        <v>4.4054</v>
+        <v>1.2589</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1311</v>
+        <v>-0.2114</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9962</v>
+        <v>0.6045</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8651</v>
+        <v>-0.8159</v>
       </c>
       <c r="G21" t="n">
         <v>2.2207</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4668</v>
+        <v>0.1244</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5609</v>
+        <v>0.1691</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.094</v>
+        <v>-0.0448</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2594</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2966</v>
+        <v>-1.5899</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2597</v>
+        <v>-2.6515</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9631</v>
+        <v>1.0616</v>
       </c>
       <c r="G22" t="n">
         <v>0.12</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0.06569999999999999</v>
+        <v>-0.2276</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1816</v>
+        <v>-0.2101</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1159</v>
+        <v>-0.0174</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8671</v>
+        <v>-2.4176</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0076</v>
+        <v>0.1882</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8595</v>
+        <v>-2.6058</v>
       </c>
       <c r="G23" t="n">
         <v>-0.729</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5316</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0584</v>
+        <v>0.1374</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1405</v>
+        <v>0.3942</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1466</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6547</v>
+        <v>-3.6312</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1421</v>
+        <v>-3.9463</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4874</v>
+        <v>0.3151</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2553</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0828</v>
+        <v>0.1063</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2313</v>
+        <v>-0.0354</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3141</v>
+        <v>0.1418</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6082</v>
+        <v>-4.0929</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6401</v>
+        <v>-3.3463</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9681</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6098</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.387</v>
+        <v>0.1284</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1977</v>
+        <v>0.0961</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1893</v>
+        <v>0.0323</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3144</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.6464</v>
+        <v>-4.7136</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3938</v>
+        <v>-2.9041</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2526</v>
+        <v>-1.8094</v>
       </c>
       <c r="G26" t="n">
         <v>0.1437</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1781</v>
+        <v>-0.2453</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.669</v>
+        <v>-0.1794</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5091</v>
+        <v>-0.0659</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2033</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,73 +2515,73 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8645</v>
+        <v>-5.5991</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.9213</v>
+        <v>-4.9391</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.9432</v>
+        <v>-0.66</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.2633</v>
+        <v>-1.4379</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.4047</v>
+        <v>-1.4026</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.8586</v>
+        <v>-0.0353</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.2481</v>
+        <v>-1.1192</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.3108</v>
+        <v>-0.4771</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.9372</v>
+        <v>-0.6422</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.0152</v>
+        <v>-0.3187</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0938</v>
+        <v>-0.9255</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.9214</v>
+        <v>0.6069</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1117</v>
+        <v>-1.297</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.297</v>
+        <v>-2.9646</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S27" t="n">
-        <v>1.1759</v>
+        <v>-0.9759</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9949</v>
+        <v>-0.8552</v>
       </c>
       <c r="U27" t="n">
-        <v>0.181</v>
+        <v>-0.1206</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.8888</v>
+        <v>-1.8883</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.5177</v>
+        <v>-1.8883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,67 +2593,67 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.2697</v>
+        <v>-6.3708</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.2328</v>
+        <v>-4.5089</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0368</v>
+        <v>-1.8619</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.4379</v>
+        <v>-6.2633</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.4026</v>
+        <v>-3.4047</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0353</v>
+        <v>-2.8586</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.1192</v>
+        <v>-4.2481</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.4771</v>
+        <v>-2.3108</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.6422</v>
+        <v>-1.9372</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3187</v>
+        <v>-2.0152</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.9255</v>
+        <v>-1.0938</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6069</v>
+        <v>-0.9214</v>
       </c>
       <c r="P28" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="Q28" t="n">
         <v>-1.297</v>
       </c>
-      <c r="Q28" t="n">
-        <v>-2.9646</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.6464</v>
+        <v>0.6696</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.149</v>
+        <v>0.4073</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.4974</v>
+        <v>0.2624</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.8883</v>
+        <v>-1.8888</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X28" t="n">
-        <v>-1.8883</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="29">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-17.7089</v>
+        <v>-17.0563</v>
       </c>
       <c r="E29" t="n">
-        <v>-13.2699</v>
+        <v>-13.2702</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.4389</v>
+        <v>-3.786</v>
       </c>
       <c r="G29" t="n">
         <v>-11.1357</v>
@@ -2686,7 +2686,7 @@
         <v>-4.57</v>
       </c>
       <c r="I29" t="n">
-        <v>-6.565700000000001</v>
+        <v>-6.5657</v>
       </c>
       <c r="J29" t="n">
         <v>-3.2959</v>
@@ -2701,13 +2701,13 @@
         <v>-7.839599999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>-5.613900000000001</v>
+        <v>-5.6139</v>
       </c>
       <c r="O29" t="n">
         <v>-2.2256</v>
       </c>
       <c r="P29" t="n">
-        <v>-7.4114</v>
+        <v>-7.411400000000001</v>
       </c>
       <c r="Q29" t="n">
         <v>-20.3817</v>
@@ -2716,16 +2716,16 @@
         <v>12.9702</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.1055999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.9199000000000002</v>
+        <v>-0.9200000000000002</v>
       </c>
       <c r="U29" t="n">
-        <v>0.8144000000000002</v>
+        <v>1.4674</v>
       </c>
       <c r="V29" t="n">
-        <v>0.9439000000000002</v>
+        <v>0.9439</v>
       </c>
       <c r="W29" t="n">
         <v>11.3275</v>
